--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -237,7 +237,7 @@
     <t>Pass:6 Fail:0 Skipped:1 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-07-27</t>
+    <t>Last Updated: 2026-07-30</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
   <si>
     <t>TC ID</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Pass</t>
+    <t/>
   </si>
   <si>
     <t>On the Search screen with the grid loaded (office 1604)</t>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>The browser download event fires and the CSV file download begins.</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>2. Read the downloaded file's suggested filename</t>
@@ -234,10 +231,10 @@
     <t>Automated: 7 / Pending: 0</t>
   </si>
   <si>
-    <t>Pass:6 Fail:0 Skipped:1 Blocked:0</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-07-30</t>
+    <t>Not run in this delivery</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-07</t>
   </si>
 </sst>
 </file>
@@ -636,7 +633,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="35" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
@@ -720,56 +717,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -778,7 +775,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -796,62 +793,62 @@
         <v>22</v>
       </c>
       <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
         <v>31</v>
       </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s">
         <v>33</v>
       </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -860,7 +857,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -878,103 +875,103 @@
         <v>22</v>
       </c>
       <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
         <v>37</v>
       </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" t="s">
         <v>39</v>
       </c>
-      <c r="L7" t="s">
-        <v>40</v>
-      </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" t="s">
         <v>41</v>
       </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
         <v>43</v>
-      </c>
-      <c r="B9" t="s">
-        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -983,7 +980,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -1001,62 +998,62 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" t="s">
         <v>45</v>
       </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" t="s">
         <v>47</v>
       </c>
-      <c r="L10" t="s">
-        <v>48</v>
-      </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s">
         <v>49</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -1083,62 +1080,62 @@
         <v>22</v>
       </c>
       <c r="K11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" t="s">
         <v>51</v>
       </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" t="s">
         <v>53</v>
       </c>
-      <c r="L12" t="s">
-        <v>54</v>
-      </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1147,7 +1144,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -1165,62 +1162,62 @@
         <v>22</v>
       </c>
       <c r="K13" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" t="s">
         <v>57</v>
       </c>
-      <c r="L13" t="s">
-        <v>58</v>
-      </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" t="s">
         <v>59</v>
       </c>
-      <c r="L14" t="s">
-        <v>60</v>
-      </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1229,7 +1226,7 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1241,101 +1238,101 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" t="s">
         <v>63</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>64</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>65</v>
       </c>
-      <c r="L15" t="s">
-        <v>66</v>
-      </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" t="s">
         <v>67</v>
       </c>
-      <c r="L16" t="s">
-        <v>68</v>
-      </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_pricing_loc_export" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="75">
   <si>
     <t>TC ID</t>
   </si>
@@ -79,16 +80,19 @@
     <t>Automated</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>On the Search screen with the grid loaded (office 1604)</t>
+  </si>
+  <si>
+    <t>1. Click "Loc Pricing Export" and wait for the browser download event to fire</t>
+  </si>
+  <si>
+    <t>The browser download event fires and the CSV file download begins.</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>On the Search screen with the grid loaded (office 1604)</t>
-  </si>
-  <si>
-    <t>1. Click "Loc Pricing Export" and wait for the browser download event to fire</t>
-  </si>
-  <si>
-    <t>The browser download event fires and the CSV file download begins.</t>
   </si>
   <si>
     <t>2. Read the downloaded file's suggested filename</t>
@@ -231,10 +235,13 @@
     <t>Automated: 7 / Pending: 0</t>
   </si>
   <si>
-    <t>Not run in this delivery</t>
-  </si>
-  <si>
-    <t>Last Updated: 2026-08-07</t>
+    <t>Pass:6 Fail:0 Skipped:1 Blocked:0</t>
+  </si>
+  <si>
+    <t>Last Updated: 2026-08-12</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -633,7 +640,7 @@
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="9" max="9" width="35" customWidth="1"/>
     <col min="10" max="12" width="80" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
@@ -717,56 +724,56 @@
         <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -775,7 +782,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
@@ -793,62 +800,62 @@
         <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -857,7 +864,7 @@
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
@@ -875,103 +882,103 @@
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
@@ -980,7 +987,7 @@
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
@@ -998,62 +1005,62 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
@@ -1080,62 +1087,62 @@
         <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
@@ -1144,7 +1151,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
@@ -1162,62 +1169,62 @@
         <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -1226,7 +1233,7 @@
         <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1238,101 +1245,117 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -241,7 +241,7 @@
     <t>Last Updated: 2026-08-12</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
+++ b/clients/encore/testcases/corporate-pricing/corporate-pricing-loc-export.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_pricing_loc_export" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="74">
   <si>
     <t>TC ID</t>
   </si>
@@ -239,9 +238,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-08-12</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -1346,20 +1342,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>